--- a/output/pdf_financials_xlsx/LME.xlsx
+++ b/output/pdf_financials_xlsx/LME.xlsx
@@ -6231,34 +6231,34 @@
         <v>4.512001</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>5.459699</v>
+        <v>5.642501</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>5.899852</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>6.127157</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>6.301178</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>6.365465</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>6.378067</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>6.399429</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>6.40534</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>4.123618</v>
+        <v>7.853168</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>4.145062</v>
+        <v>9.799132999999999</v>
       </c>
       <c r="N92" s="3" t="n">
         <v>4.214842</v>
@@ -11604,7 +11604,11 @@
           <t>Warrants reserve 9</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -12752,7 +12756,11 @@
           <t>Warrants reserve</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -12854,7 +12862,11 @@
           <t>Share based payments reserve</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -16730,7 +16742,11 @@
           <t>Warrants reserve</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -16832,7 +16848,11 @@
           <t>Share based payments reserve</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -18048,7 +18068,11 @@
           <t>Warrants reserve</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -18144,7 +18168,11 @@
           <t>Share based payments reserve</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -19928,7 +19956,11 @@
           <t>Warrants reserve (Note 10) 2,191,568</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -20028,7 +20060,11 @@
           <t>Share based payments reserve (Note 10) 3,708,284</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/LME.xlsx
+++ b/output/pdf_financials_xlsx/LME.xlsx
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.036736</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.002807</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000987</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1083,13 +1083,13 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>6.3e-05</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>1.6e-05</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.000188</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
@@ -1104,13 +1104,13 @@
         <v>0</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.386305</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-0.448383</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>-0.249057</v>
       </c>
     </row>
     <row r="13">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.858738</v>
+        <v>-1.895474</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.408783</v>
+        <v>-0.41159</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.714486</v>
+        <v>1.713499</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-3.233464</v>
@@ -2112,13 +2112,13 @@
         <v>0.738264</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.369864</v>
+        <v>-0.369927</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.306658</v>
+        <v>-0.306674</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.435378</v>
+        <v>-1.435566</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-2.254633</v>
@@ -2133,13 +2133,13 @@
         <v>-4.653523</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-3.086043</v>
+        <v>-2.699738</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-2.916429</v>
+        <v>-2.468046</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-4.528183</v>
+        <v>-4.279126</v>
       </c>
     </row>
     <row r="28">
@@ -2210,13 +2210,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.858738</v>
+        <v>-1.895474</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.408783</v>
+        <v>-0.41159</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.714486</v>
+        <v>1.713499</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-3.233464</v>
@@ -2234,13 +2234,13 @@
         <v>0.738264</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.369864</v>
+        <v>-0.369927</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.306658</v>
+        <v>-0.306674</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.435378</v>
+        <v>-1.435566</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-2.254633</v>
@@ -2255,13 +2255,13 @@
         <v>-4.653523</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-3.086043</v>
+        <v>-2.699738</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-2.916429</v>
+        <v>-2.468046</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-4.528183</v>
+        <v>-4.279126</v>
       </c>
     </row>
     <row r="30">
@@ -2533,46 +2533,46 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.388736</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.162423</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.162423</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.527954</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.562495</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.391492</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.047582</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.105145</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.021483</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.017984</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.064785</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.672805</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.547348</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>6.857589</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>7.474144</v>
@@ -2655,46 +2655,46 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.388736</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.162423</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.162423</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.527954</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.562495</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.391492</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.047582</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.105145</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.021483</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.017984</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.064785</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.672805</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.547348</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>6.857589</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>7.474144</v>
@@ -3387,46 +3387,46 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.399737</v>
+        <v>0.011001</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.172255</v>
+        <v>0.009832</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.172255</v>
+        <v>0.009832</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.063769</v>
+        <v>0.535815</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.680601</v>
+        <v>0.118106</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.417534</v>
+        <v>0.026042</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.053497</v>
+        <v>0.005915</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.105146</v>
+        <v>1e-06</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.024444</v>
+        <v>0.002961</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.017984</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.224785</v>
+        <v>0.16</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.02227</v>
+        <v>1.349465</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>2.763379</v>
+        <v>1.216031</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>9.869897</v>
+        <v>3.012308</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>1.671143</v>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -11930,7 +11930,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -18892,7 +18892,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -20378,7 +20378,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
@@ -43092,7 +43092,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -50664,7 +50664,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
@@ -53050,7 +53050,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
@@ -53864,7 +53864,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -56270,7 +56270,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E454" s="5" t="n">

--- a/output/pdf_financials_xlsx/LME.xlsx
+++ b/output/pdf_financials_xlsx/LME.xlsx
@@ -6655,7 +6655,7 @@
         <v>-1.231125</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>-2.726992</v>
+        <v>0.738264</v>
       </c>
       <c r="J99" s="3" t="n">
         <v>-0.369864</v>
@@ -7366,7 +7366,7 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001473</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -7652,16 +7652,16 @@
         <v>0</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>0.048155</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>0.012316</v>
       </c>
       <c r="R115" s="3" t="n">
-        <v>0</v>
+        <v>0.025831</v>
       </c>
       <c r="S115" s="3" t="n">
-        <v>0</v>
+        <v>0.031938</v>
       </c>
     </row>
     <row r="116">
@@ -8853,7 +8853,7 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001473</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -24050,7 +24050,11 @@
           <t>Proceeds from the sale of marketable securities</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -25692,7 +25696,11 @@
           <t>Proceeds from the sale of marketable securities (note 7)</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -31936,7 +31944,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -41274,7 +41286,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr"/>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E310" s="5" t="n">
         <v>-0.001473</v>
       </c>
@@ -57114,7 +57130,11 @@
           <t>Net earnings (loss)</t>
         </is>
       </c>
-      <c r="D462" t="inlineStr"/>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E462" t="inlineStr">
         <is>
           <t>-</t>
